--- a/optimized_version/metadata/validation_testing_metrics/rbfnn_vs_benchmark_mape_comparison.xlsx
+++ b/optimized_version/metadata/validation_testing_metrics/rbfnn_vs_benchmark_mape_comparison.xlsx
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.313742647047742</v>
+        <v>3.44846086233487</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -493,13 +493,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3.434675445626739</v>
+        <v>3.451840791241192</v>
       </c>
       <c r="E2" t="n">
-        <v>0.120932798578997</v>
+        <v>0.003379928906321883</v>
       </c>
       <c r="F2" t="n">
-        <v>3.434813729089702</v>
+        <v>3.472312585221351</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -507,10 +507,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>3.486362417005193</v>
+        <v>3.486362417005194</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05154868791549072</v>
+        <v>0.01404983178384311</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
@@ -529,7 +529,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.080237395346142</v>
+        <v>1.080237143771774</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -537,13 +537,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.720696696292816</v>
+        <v>1.744494832966965</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6404593009466744</v>
+        <v>0.664257689195191</v>
       </c>
       <c r="F3" t="n">
-        <v>1.372393407091134</v>
+        <v>1.372393407124575</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -554,7 +554,7 @@
         <v>2.161182022518592</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7887886154274579</v>
+        <v>0.7887886153940171</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.826760962489566</v>
+        <v>0.8267609536299209</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -581,13 +581,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.631781368537392</v>
+        <v>1.71745827658513</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8050204060478261</v>
+        <v>0.8906973229552092</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6106872917110348</v>
+        <v>0.610687291764428</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.071541685667849</v>
+        <v>1.05126148122372</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4608543939568143</v>
+        <v>0.4405741894592919</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.140856265711159</v>
+        <v>4.090822640338563</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4.164354919883476</v>
+        <v>4.180765718437955</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02349865417231722</v>
+        <v>0.08994307809939261</v>
       </c>
       <c r="F5" t="n">
-        <v>4.043801373118373</v>
+        <v>4.039603028830673</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
         <v>4.200484513643534</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1566831405251614</v>
+        <v>0.1608814848128617</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.412584472137003</v>
+        <v>2.412584472531949</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2.691804783297085</v>
+        <v>2.664091660721063</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2792203111600817</v>
+        <v>0.2515071881891142</v>
       </c>
       <c r="F6" t="n">
-        <v>1.404527208181197</v>
+        <v>1.404527208907398</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -683,10 +683,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>19.87941386644246</v>
+        <v>19.87941386644245</v>
       </c>
       <c r="I6" t="n">
-        <v>18.47488665826126</v>
+        <v>18.47488665753505</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.829444573472466</v>
+        <v>3.806185782118045</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4.074631372425127</v>
+        <v>4.083274772187985</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2451867989526613</v>
+        <v>0.2770889900699398</v>
       </c>
       <c r="F7" t="n">
-        <v>4.221972725718088</v>
+        <v>4.20930169631497</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>4.294212888621111</v>
+        <v>4.294212888621112</v>
       </c>
       <c r="I7" t="n">
-        <v>0.07224016290302249</v>
+        <v>0.08491119230614164</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
